--- a/output/pdf_financials_xlsx/AII.xlsx
+++ b/output/pdf_financials_xlsx/AII.xlsx
@@ -1047,10 +1047,10 @@
         <v>0</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>1.539</v>
       </c>
     </row>
     <row r="13">
@@ -1960,10 +1960,10 @@
         <v>-0.00877</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-15.926</v>
+        <v>-15.928</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-161.443</v>
+        <v>-162.982</v>
       </c>
     </row>
     <row r="28">
@@ -2070,10 +2070,10 @@
         <v>-0.007693</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-14.806</v>
+        <v>-14.808</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-160.4</v>
+        <v>-161.939</v>
       </c>
     </row>
     <row r="30">
@@ -2129,10 +2129,10 @@
         <v>-34.17592181252777</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-51.34554029685115</v>
+        <v>-51.35247607157719</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-493.3259518976441</v>
+        <v>-498.0592975333702</v>
       </c>
     </row>
     <row r="31">
@@ -2289,28 +2289,28 @@
         <v>0.004473</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.008721</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.001496</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.002372</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.001048</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.008442</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.022019</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>7.83</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>268.409</v>
       </c>
     </row>
     <row r="35">
@@ -2403,28 +2403,28 @@
         <v>0.004473</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.008721</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.001496</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.002372</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.001048</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.008442</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.022019</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>7.83</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>268.409</v>
       </c>
     </row>
     <row r="37">
@@ -3087,28 +3087,28 @@
         <v>0.001284</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.012097</v>
+        <v>0.003376</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.002939</v>
+        <v>0.001443</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.003299</v>
+        <v>0.000927</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.00252</v>
+        <v>0.001472</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.012913</v>
+        <v>0.004471</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.025729</v>
+        <v>0.00371</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>10.911</v>
+        <v>3.081</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>274.417</v>
+        <v>6.008</v>
       </c>
     </row>
     <row r="49">
@@ -7338,7 +7338,7 @@
         <v>0</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-4.7e-05</v>
       </c>
       <c r="F124" s="3" t="n">
         <v>-0.002173</v>
@@ -7393,7 +7393,7 @@
         <v>0</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-4.7e-05</v>
       </c>
       <c r="F125" s="3" t="n">
         <v>-0.002173</v>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -11062,7 +11062,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -35268,7 +35268,11 @@
           <t>Capital lease payments</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr"/>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E294" t="inlineStr">
         <is>
           <t>-</t>
@@ -40808,7 +40812,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -41256,7 +41260,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -44946,7 +44950,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
